--- a/Collections/EURO/San_Marino/#EURO#San_Marino#Commemorative#[2004-present]#UNC.xlsx
+++ b/Collections/EURO/San_Marino/#EURO#San_Marino#Commemorative#[2004-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\San_Marino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DCA9B8-970B-4629-B7AF-238F072DCC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49954522-9A50-4FC7-ABCA-FBE312450785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Year</t>
   </si>
@@ -341,6 +344,15 @@
   </si>
   <si>
     <t>550th Anniversary - Birth of Michelangelo</t>
+  </si>
+  <si>
+    <t>10th page</t>
+  </si>
+  <si>
+    <t>800th Anniversary - Death of Francis of Assisi</t>
+  </si>
+  <si>
+    <t>450th Anniversary - Death of Titian</t>
   </si>
 </sst>
 </file>
@@ -954,7 +966,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1009,9 +1029,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2213,7 +2233,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>2025</v>
       </c>
@@ -2240,10 +2260,50 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H37" s="1"/>
+      <c r="A37" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" s="30">
+        <v>0</v>
+      </c>
+      <c r="H37" s="39" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H38" s="1"/>
+      <c r="A38" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="57">
+        <v>0</v>
+      </c>
+      <c r="H38" s="39"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2253,11 +2313,28 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G3:G34">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G34">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2269,12 +2346,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
+  <conditionalFormatting sqref="G36">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
+  <conditionalFormatting sqref="G36">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2286,12 +2363,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
+  <conditionalFormatting sqref="G37:G38">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
+  <conditionalFormatting sqref="G37:G38">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
